--- a/src/Excelsior.Tests/RowHeights.MaxRowHeightFluentZeroRows.verified.xlsx
+++ b/src/Excelsior.Tests/RowHeights.MaxRowHeightFluentZeroRows.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -66,4 +66,13 @@
   </sheetData>
   <autoFilter ref="A1:B1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Title"/>
+    <column index="2" property="Body"/>
+  </sheet>
+</columnMetadata>
 </file>